--- a/results/Network_Topology_01/results_request_20.xlsx
+++ b/results/Network_Topology_01/results_request_20.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,52 +460,28 @@
           <t>ILP_RCWA_SLC_03</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ILP_RWA_01</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ILP_RWA_02</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ILP_RWA_03</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="C2" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.16</v>
+        <v>1.29</v>
       </c>
       <c r="E2" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="F2" t="n">
         <v>0.24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -513,31 +489,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.85</v>
+        <v>0.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="D3" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="E3" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="F3" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H3" t="n">
         <v>0.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -545,31 +512,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="D4" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="E4" t="n">
-        <v>1.14</v>
+        <v>0.57</v>
       </c>
       <c r="F4" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="5">
@@ -577,31 +535,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="C5" t="n">
-        <v>1.57</v>
+        <v>0.24</v>
       </c>
       <c r="D5" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="E5" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F5" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="6">
@@ -609,31 +558,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="D6" t="n">
-        <v>2.51</v>
+        <v>1.98</v>
       </c>
       <c r="E6" t="n">
-        <v>0.62</v>
+        <v>1.1</v>
       </c>
       <c r="F6" t="n">
         <v>0.19</v>
       </c>
       <c r="G6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="7">
@@ -641,31 +581,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.43</v>
+        <v>2.81</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.59</v>
+        <v>1.47</v>
       </c>
       <c r="F7" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="8">
@@ -673,31 +604,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.68</v>
+        <v>0.89</v>
       </c>
       <c r="C8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.32</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.16</v>
       </c>
     </row>
     <row r="9">
@@ -705,30 +627,21 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="C9" t="n">
-        <v>1.01</v>
+        <v>0.52</v>
       </c>
       <c r="D9" t="n">
-        <v>2.35</v>
+        <v>1.21</v>
       </c>
       <c r="E9" t="n">
-        <v>0.59</v>
+        <v>1.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J9" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -737,31 +650,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.69</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11">
@@ -769,31 +673,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="C11" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2.35</v>
       </c>
       <c r="E11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="12">
@@ -803,31 +698,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.084</v>
+        <v>1.8</v>
       </c>
       <c r="C12" t="n">
-        <v>0.651</v>
+        <v>0.39</v>
       </c>
       <c r="D12" t="n">
-        <v>1.436</v>
+        <v>1.45</v>
       </c>
       <c r="E12" t="n">
-        <v>0.666</v>
+        <v>0.751</v>
       </c>
       <c r="F12" t="n">
-        <v>0.226</v>
+        <v>0.18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.145</v>
+        <v>0.334</v>
       </c>
     </row>
   </sheetData>
@@ -841,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,21 +761,6 @@
           <t>ILP_RCWA_SLC_03</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ILP_RWA_01</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ILP_RWA_02</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ILP_RWA_03</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -913,46 +784,28 @@
       <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -977,15 +830,6 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1009,46 +853,28 @@
       <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1073,15 +899,6 @@
       <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1105,46 +922,28 @@
       <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1152,31 +951,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1201,15 +991,6 @@
       <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1218,31 +999,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
